--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CellValues.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CellValues.xlsx
@@ -61,7 +61,7 @@
     <x:numFmt numFmtId="1" formatCode="yyyy-MMM-dd"/>
     <x:numFmt numFmtId="2" formatCode="#,##0.00"/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="3">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -71,6 +71,13 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CellValues.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CellValues.xlsx
@@ -462,12 +462,12 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="13.550625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.700625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="14.840625000000001" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="21.130625000000002" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="21.700625" style="0" customWidth="1"/>
-    <x:col min="7" max="7" width="22.130625000000002" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="12.270625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.920625000000001" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13.250625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="19.660625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="21.270625" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20.560625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:7">

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CellValues.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CellValues.xlsx
@@ -119,47 +119,47 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="6">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="46" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="6">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CellValues.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CellValues.xlsx
@@ -463,7 +463,7 @@
   <x:cols>
     <x:col min="1" max="1" width="9.140625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="12.270625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.920625000000001" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.920625" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="13.250625" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="19.660625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="21.270625" style="0" customWidth="1"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CellValues.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Misc/CellValues.xlsx
@@ -58,8 +58,8 @@
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="3">
     <x:numFmt numFmtId="0" formatCode=""/>
-    <x:numFmt numFmtId="1" formatCode="yyyy-MMM-dd"/>
-    <x:numFmt numFmtId="2" formatCode="#,##0.00"/>
+    <x:numFmt numFmtId="165" formatCode="yyyy-MMM-dd"/>
+    <x:numFmt numFmtId="166" formatCode="#,##0.00"/>
   </x:numFmts>
   <x:fonts count="3">
     <x:font>
@@ -125,13 +125,13 @@
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="14" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="46" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
@@ -147,7 +147,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -155,7 +155,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
